--- a/utils/planilhas_competidores/Lorenzo_previsoes.xlsx
+++ b/utils/planilhas_competidores/Lorenzo_previsoes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\utils\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479BCCBB-02A7-4F37-9E9E-F3D4019DD04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D4F55A-47AE-455D-A37C-02708091A394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1916,7 +1916,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>84</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>90</v>
       </c>
@@ -1961,8 +1961,14 @@
       <c r="G50" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50">
+        <v>3</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>90</v>
       </c>
@@ -1985,7 +1991,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>90</v>
       </c>
@@ -2008,7 +2014,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>90</v>
       </c>
@@ -2031,7 +2037,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>90</v>
       </c>
@@ -2054,7 +2060,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>90</v>
       </c>
@@ -2077,7 +2083,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>98</v>
       </c>
@@ -2100,7 +2106,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>98</v>
       </c>
@@ -2123,7 +2129,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>98</v>
       </c>
@@ -2146,7 +2152,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>98</v>
       </c>
@@ -2169,7 +2175,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>98</v>
       </c>
@@ -2192,7 +2198,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>98</v>
       </c>
@@ -2215,7 +2221,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>105</v>
       </c>
@@ -2238,7 +2244,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -2261,7 +2267,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>105</v>
       </c>
